--- a/data/trans_orig/IP31B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31B_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4954</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8913</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5700</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12220</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18947</t>
+          <t>14050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24575</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18817</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31368</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>32338</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23760</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>40744</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45,29%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>57,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>26083</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21134</t>
+          <t>20689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>31930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>60941</t>
+          <t>50658</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>42335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72903</t>
+          <t>59286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21317</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15837</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>27571</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>35,37%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>45,75%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17694</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25244</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,36%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>15529</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>20609</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>36847</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>29421</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56939</t>
+          <t>45141</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3472</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10701</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10219</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3523</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24369</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,13%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6558</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5450</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2671</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10194</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6974</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7226</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2550</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13572</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>15860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56727</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46679</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67701</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>49284</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25454</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>65948</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>40,01%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,66%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60788</t>
+          <t>48118</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48232</t>
+          <t>39335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72817</t>
+          <t>56671</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>110072</t>
+          <t>104845</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74747</t>
+          <t>90616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130438</t>
+          <t>118277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>55,82%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>44403</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34548</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56285</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>38,73%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>49,09%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>60800</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>39542</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>90440</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>49,35%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>73,41%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49149</t>
+          <t>36183</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37364</t>
+          <t>27802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62242</t>
+          <t>45007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>109950</t>
+          <t>80586</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86338</t>
+          <t>66627</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>153325</t>
+          <t>94606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12444</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1457</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4336</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4457</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2358</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7809</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4423</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1490</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10362</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>114652</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>114652</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>114652</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>123190</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>123190</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>123190</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>249217</t>
+          <t>211883</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>249217</t>
+          <t>211883</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>249217</t>
+          <t>211883</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5708</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9958</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8594</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4803</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13455</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>13538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26991</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21363</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33055</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>37,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>22409</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17187</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28546</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>40,34%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>27645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>52708</t>
+          <t>48861</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43828</t>
+          <t>41227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61354</t>
+          <t>56682</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20334</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14708</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26195</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>35,49%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>25,67%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>45,72%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>20060</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14349</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>25383</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>36,11%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>45,69%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29005</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>40238</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34886</t>
+          <t>32840</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51503</t>
+          <t>48145</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2589</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5943</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3552</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1529</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7434</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13252</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4739</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3780</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6371</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>944</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12369</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6188</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>20791</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>18,4%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>30,93%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>15853</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>10306</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>24226</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>23,11%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>35,32%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>24237</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>28484</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40306</t>
+          <t>40232</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>40031</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>29905</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>50763</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>59,55%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>44,49%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>75,51%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>34638</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>27300</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>41992</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>50,5%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>39,8%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>61,22%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>43067</t>
+          <t>35573</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32487</t>
+          <t>27794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55538</t>
+          <t>43869</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>77706</t>
+          <t>75603</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64519</t>
+          <t>62929</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93715</t>
+          <t>88492</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10698</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5379</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>19058</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>28,35%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>11183</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6537</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>17228</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>16,3%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>18062</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>22041</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32098</t>
+          <t>32224</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4951</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9812</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>14,6%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>4944</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>67223</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>67223</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>67223</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>68597</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>68597</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>68597</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>71552</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>71552</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>71552</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>140149</t>
+          <t>136496</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>140149</t>
+          <t>136496</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>140149</t>
+          <t>136496</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>16719</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>11659</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>21362</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>42,24%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>29,46%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>53,97%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>15984</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>12150</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>20042</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>46,74%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>35,53%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>58,6%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22897</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>33956</t>
+          <t>33358</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27526</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40369</t>
+          <t>40005</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,38%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>22388</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>17970</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>27303</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>56,57%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>45,4%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>68,98%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>17639</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>13580</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>21559</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>51,58%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>39,71%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>63,04%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>22161</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27147</t>
+          <t>22222</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>39800</t>
+          <t>40501</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33087</t>
+          <t>33685</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46149</t>
+          <t>46852</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>62,51%</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>472</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>619</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>4779</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>1178</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>4033</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>1698</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>4839</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>14407</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>9721</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>19619</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>30,52%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>41,56%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>18314</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>13630</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>23518</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>41,35%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>30,78%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>53,1%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>16012</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>24219</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>34326</t>
+          <t>33483</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26952</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>41942</t>
+          <t>40962</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>22159</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>27618</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>46,94%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>36,01%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>58,5%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>20252</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>14996</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>25206</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>45,73%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>33,86%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>56,91%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>24590</t>
+          <t>20232</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29916</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>44841</t>
+          <t>42391</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>37554</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>49423</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>6204</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>11651</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>13,14%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>24,68%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2430</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>5568</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17554</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2819</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>5526</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2116</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>5528</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>514</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>27523</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>19755</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>36735</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>19,71%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>26,31%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>26783</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>19203</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>34811</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>28680</t>
+          <t>27150</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>38636</t>
+          <t>34694</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>55462</t>
+          <t>54673</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>43248</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>69176</t>
+          <t>67154</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>63872</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>52255</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>74322</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>45,74%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>37,42%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>53,23%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>62231</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>52778</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>71884</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>50,47%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>58,3%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>70567</t>
+          <t>61658</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>57327</t>
+          <t>51969</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>71172</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>132798</t>
+          <t>125531</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>114736</t>
+          <t>110631</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>149496</t>
+          <t>140771</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>37402</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>28001</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>50123</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>26,79%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>35,9%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>29105</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>22057</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>38713</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>31,4%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>61212</t>
+          <t>35762</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>73217</t>
+          <t>65062</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>59973</t>
+          <t>53230</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>92064</t>
+          <t>79868</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>6905</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>3455</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>13136</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>1938</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>5495</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>484</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>14088</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>139628</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>139628</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>139628</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>123305</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>123305</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>123305</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>154074</t>
+          <t>121482</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>154074</t>
+          <t>121482</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>154074</t>
+          <t>121482</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>277378</t>
+          <t>261110</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>277378</t>
+          <t>261110</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>277378</t>
+          <t>261110</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>41817</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>32577</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>53295</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>20,73%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>40677</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>32493</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>50282</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>39,08%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>40270</t>
+          <t>45489</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>31306</t>
+          <t>36183</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>51150</t>
+          <t>56227</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>80947</t>
+          <t>87306</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>69449</t>
+          <t>74170</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>95955</t>
+          <t>103243</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -5607,72 +5607,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>95472</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>84629</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>106634</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>60,76%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>53,86%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>67,86%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>70621</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>60228</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>78802</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>54,89%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>46,81%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>61,25%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>93623</t>
+          <t>73668</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>82260</t>
+          <t>62207</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>103342</t>
+          <t>84451</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>164244</t>
+          <t>169141</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>148842</t>
+          <t>153438</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>176677</t>
+          <t>183791</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,29%</t>
         </is>
       </c>
     </row>
@@ -5720,72 +5720,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>9812</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>5165</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>16709</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>12460</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>7370</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>19634</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>23484</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>32455</t>
+          <t>34714</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -5833,72 +5833,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>6091</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>10930</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>3097</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>7166</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -5946,72 +5946,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>3944</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1643</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>8472</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>1809</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>4926</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>488</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>112666</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>95658</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>130745</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>121996</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>100409</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>140216</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>18,79%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>21,6%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>115285</t>
+          <t>126614</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>98810</t>
+          <t>109025</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>134867</t>
+          <t>144966</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>239281</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>212258</t>
+          <t>213495</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>266073</t>
+          <t>264840</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>344463</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>319036</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>371426</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>50,43%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>46,71%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>54,38%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>307476</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>265085</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>333648</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>40,83%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>365120</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>337665</t>
+          <t>282669</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>395340</t>
+          <t>326544</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>672595</t>
+          <t>648622</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>620907</t>
+          <t>613763</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>712488</t>
+          <t>686937</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>166597</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>146588</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>189356</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>172131</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>144335</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>240155</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>36,99%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>189597</t>
+          <t>145143</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>165196</t>
+          <t>128779</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>217037</t>
+          <t>163508</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>361728</t>
+          <t>311740</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>325266</t>
+          <t>286448</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>432378</t>
+          <t>341675</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>37035</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>28583</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>48799</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>24669</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>16092</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>47211</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>43287</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>32460</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>67956</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>53014</t>
+          <t>43681</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>91551</t>
+          <t>67970</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>22227</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>15446</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>30452</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>22927</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>16404</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>32428</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>14809</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>28927</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>42736</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>38916</t>
+          <t>34292</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>61916</t>
+          <t>55663</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>908</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
